--- a/harmonized_tables_advp/from_29274321_table2_v1.xlsx
+++ b/harmonized_tables_advp/from_29274321_table2_v1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT11"/>
+  <dimension ref="A1:AV17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,87 +564,97 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>P-value note</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>BP(Position)</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>RA 1(Reported Allele 1)</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>RA 2(Reported Allele 2)</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Note on alleles and AF</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>ReportedAF(MAF)</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>AFincases</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>AFincontrols</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Effect Size Type (OR or Beta)</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>EffectSize(altvsref)</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>95%ConfidenceInterval</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Confirmed affected genes, causal variants, evidence</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Genome build (hg18/hg37/hg38)</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Pubmed PMID</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>PMCID</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Table Ref in paper</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Table links</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>LocusName</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>Comment</t>
         </is>
       </c>
     </row>
@@ -669,7 +679,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>eQTL comparison table; likely supporting/comparison result rather than new ADVP association result</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -710,10 +724,8 @@
           <t>ADNI</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>757</t>
-        </is>
+      <c r="N2" t="n">
+        <v>757</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -728,68 +740,94 @@
           <t>European ancestry</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>adsfasd</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>eQTL</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Hippocampus</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Fron Cor</t>
+          <t>rs10775009</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>0.09</v>
+      </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Frontal Cortex</t>
+        </is>
+      </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr">
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL2" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Frontal Cortex</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>0.09</v>
       </c>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>29274321</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr">
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>29274321</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>29274321_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>SRRM4</t>
         </is>
       </c>
+      <c r="AV2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rs2819438</t>
+          <t>rs10775009</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -807,7 +845,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>eQTL comparison table; likely supporting/comparison result rather than new ADVP association result</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -848,10 +890,8 @@
           <t>ADNI</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>757</t>
-        </is>
+      <c r="N3" t="n">
+        <v>757</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -867,62 +907,84 @@
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>eQTL</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Frontal Cortex</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Anter cingul cor</t>
+          <t>rs10775009</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>0.16</v>
+      </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Frontal Cortex</t>
+        </is>
+      </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr">
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL3" t="n">
+      <c r="AM3" t="n">
         <v>0.1</v>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Anterior cingulate cortex</t>
-        </is>
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>29274321</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr">
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>29274321</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AT3" t="inlineStr">
         <is>
           <t>29274321_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>PLD4</t>
-        </is>
-      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>SRRM4</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -945,7 +1007,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>eQTL comparison table; likely supporting/comparison result rather than new ADVP association result</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -986,10 +1052,8 @@
           <t>ADNI</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>757</t>
-        </is>
+      <c r="N4" t="n">
+        <v>757</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -1005,62 +1069,84 @@
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>eQTL</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hippocampus</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Cerebel Hemisph</t>
+          <t>rs2819438</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>0.47</v>
+      </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Anterior cingulate cortex</t>
+        </is>
+      </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr">
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL4" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Cerebellar Hemisphere</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>0.12</v>
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>29274321</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr">
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>29274321</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AT4" t="inlineStr">
         <is>
           <t>29274321_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>AHNAK2</t>
-        </is>
-      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>PLD4</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1083,7 +1169,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>eQTL comparison table; likely supporting/comparison result rather than new ADVP association result</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -1124,10 +1214,8 @@
           <t>ADNI</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>757</t>
-        </is>
+      <c r="N5" t="n">
+        <v>757</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -1145,64 +1233,82 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Hippocampus</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr"/>
+          <t>eQTL</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Anterior cingulate cortex</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Hippocampus</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Cor</t>
+          <t>rs2819438</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>0.00038</v>
+        <v>0.1</v>
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Anterior cingulate cortex</t>
+        </is>
+      </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr">
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
+      <c r="AM5" t="n">
+        <v>0.42</v>
+      </c>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>29274321</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr">
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="n">
+        <v>29274321</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>29274321_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>C14orf79</t>
-        </is>
-      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>PLD4</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1225,7 +1331,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>eQTL comparison table; likely supporting/comparison result rather than new ADVP association result</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -1266,10 +1376,8 @@
           <t>ADNI</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>757</t>
-        </is>
+      <c r="N6" t="n">
+        <v>757</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -1287,64 +1395,82 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Other brain region</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr"/>
+          <t>eQTL</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hippocampus</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Other brain region</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Cor</t>
+          <t>rs2819438</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>0.0039</v>
+        <v>0.15</v>
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Cerebellar Hemisphere</t>
+        </is>
+      </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr">
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>0.23</v>
+      </c>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>29274321</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr">
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>29274321</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AT6" t="inlineStr">
         <is>
           <t>29274321_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>C14orf79</t>
-        </is>
-      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>AHNAK2</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1367,7 +1493,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>eQTL comparison table; likely supporting/comparison result rather than new ADVP association result</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -1408,10 +1538,8 @@
           <t>ADNI</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>757</t>
-        </is>
+      <c r="N7" t="n">
+        <v>757</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -1429,64 +1557,82 @@
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Hippocampus</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr"/>
+          <t>eQTL</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Cerebellar Hemisphere</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Hippocampus</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Cerebel</t>
+          <t>rs2819438</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>0.00038</v>
+        <v>0.06</v>
       </c>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Cerebellar Hemisphere</t>
+        </is>
+      </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr">
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
+      <c r="AM7" t="n">
+        <v>-0.28</v>
+      </c>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>29274321</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr">
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>29274321</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AT7" t="inlineStr">
         <is>
           <t>29274321_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>C14orf79</t>
-        </is>
-      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>AHNAK2</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1509,7 +1655,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>eQTL comparison table; likely supporting/comparison result rather than new ADVP association result</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -1550,10 +1700,8 @@
           <t>ADNI</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>757</t>
-        </is>
+      <c r="N8" t="n">
+        <v>757</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -1571,69 +1719,87 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Other brain region</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr"/>
+          <t>eQTL</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hippocampus</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Other brain region</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Cerebel</t>
+          <t>rs2819438</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>0.006</v>
+        <v>0.00038</v>
       </c>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Cortex</t>
+        </is>
+      </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr">
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
+      <c r="AM8" t="n">
+        <v>0.44</v>
+      </c>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>29274321</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr">
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>29274321</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AT8" t="inlineStr">
         <is>
           <t>29274321_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AU8" t="inlineStr">
         <is>
           <t>C14orf79</t>
         </is>
       </c>
+      <c r="AV8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rs4921790</t>
+          <t>rs2819438</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1651,7 +1817,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>eQTL comparison table; likely supporting/comparison result rather than new ADVP association result</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -1692,10 +1862,8 @@
           <t>ADNI</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>757</t>
-        </is>
+      <c r="N9" t="n">
+        <v>757</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -1711,67 +1879,89 @@
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>eQTL</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Cortex</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Caud</t>
+          <t>rs2819438</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>0.0039</v>
+      </c>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Cortex</t>
+        </is>
+      </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr">
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Caudate</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>0.31</v>
       </c>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>29274321</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr">
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>29274321</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AT9" t="inlineStr">
         <is>
           <t>29274321_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>MTUS1</t>
-        </is>
-      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>C14orf79</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rs55653268</t>
+          <t>rs2819438</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1789,7 +1979,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>eQTL comparison table; likely supporting/comparison result rather than new ADVP association result</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -1830,10 +2024,8 @@
           <t>ADNI</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>757</t>
-        </is>
+      <c r="N10" t="n">
+        <v>757</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -1851,69 +2043,87 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Other brain region</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr"/>
+          <t>eQTL</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hippocampus</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Other brain region</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr"/>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Caud</t>
+          <t>rs2819438</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>0.0097</v>
+        <v>0.00038</v>
       </c>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Cerebellum</t>
+        </is>
+      </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr">
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
+      <c r="AM10" t="n">
+        <v>0.44</v>
+      </c>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>29274321</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr">
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="n">
+        <v>29274321</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AT10" t="inlineStr">
         <is>
           <t>29274321_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>MTUS1</t>
-        </is>
-      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>C14orf79</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rs55653268</t>
+          <t>rs2819438</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1931,7 +2141,11 @@
           <t>T00002</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>eQTL comparison table; likely supporting/comparison result rather than new ADVP association result</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>Meta-analysis</t>
@@ -1972,10 +2186,8 @@
           <t>ADNI</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>757</t>
-        </is>
+      <c r="N11" t="n">
+        <v>757</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -1991,62 +2203,1056 @@
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>eQTL</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Cerebellum</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Nucl accumb</t>
+          <t>rs2819438</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>0.006</v>
+      </c>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Cerebellum</t>
+        </is>
+      </c>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr">
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
       </c>
-      <c r="AL11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Nucleus accumbens</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>0.44</v>
       </c>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>29274321</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr">
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="n">
+        <v>29274321</v>
+      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AT11" t="inlineStr">
         <is>
           <t>29274321_table2.xlsx</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>C14orf79</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>rs4921790</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>29274321_table2_R00011</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>29274321_table2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>eQTL comparison table; likely supporting/comparison result rather than new ADVP association result</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Meta-analysis</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Meta-analysis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Imaging</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>linear regression (with covariates)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>ADNI</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ADNI</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>757</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>European ancestry</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>eQTL</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hippocampus</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>rs4921790</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Caudate</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="n">
+        <v>29274321</v>
+      </c>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>29274321_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
         <is>
           <t>MTUS1</t>
         </is>
       </c>
+      <c r="AV12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>rs4921790</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>29274321_table2_R00012</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>29274321_table2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>eQTL comparison table; likely supporting/comparison result rather than new ADVP association result</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Meta-analysis</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Meta-analysis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Imaging</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>linear regression (with covariates)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>ADNI</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ADNI</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>757</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>European ancestry</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>eQTL</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Caudate</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>rs4921790</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Caudate</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AM13" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="n">
+        <v>29274321</v>
+      </c>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>29274321_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>MTUS1</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>rs55653268</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>29274321_table2_R00013</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>29274321_table2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>eQTL comparison table; likely supporting/comparison result rather than new ADVP association result</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Meta-analysis</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Meta-analysis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Imaging</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>linear regression (with covariates)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>ADNI</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ADNI</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>757</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>European ancestry</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>eQTL</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hippocampus</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>rs55653268</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Caudate</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="n">
+        <v>29274321</v>
+      </c>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>29274321_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>MTUS1</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>rs55653268</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>29274321_table2_R00014</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>29274321_table2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>eQTL comparison table; likely supporting/comparison result rather than new ADVP association result</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Meta-analysis</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Meta-analysis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Imaging</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>linear regression (with covariates)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>ADNI</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ADNI</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>757</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>European ancestry</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>eQTL</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Caudate</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>rs55653268</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Caudate</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AM15" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="n">
+        <v>29274321</v>
+      </c>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>29274321_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>MTUS1</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>rs55653268</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>29274321_table2_R00015</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>29274321_table2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>eQTL comparison table; likely supporting/comparison result rather than new ADVP association result</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Meta-analysis</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Meta-analysis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Imaging</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>linear regression (with covariates)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>ADNI</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ADNI</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>757</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>European ancestry</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>eQTL</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hippocampus</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>rs55653268</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Nucleus accumbens</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="n">
+        <v>29274321</v>
+      </c>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>29274321_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>MTUS1</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>rs55653268</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>29274321_table2_R00016</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>29274321_table2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>T00002</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>eQTL comparison table; likely supporting/comparison result rather than new ADVP association result</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Meta-analysis</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Meta-analysis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Imaging</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>linear regression (with covariates)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>SNP-based</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>ADNI</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ADNI</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>757</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>European ancestry</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>eQTL</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Nucleus accumbens</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>rs55653268</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Nucleus accumbens</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="AM17" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="n">
+        <v>29274321</v>
+      </c>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>29274321_table2.xlsx</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>MTUS1</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
